--- a/output/roomself_excel/4011.xlsx
+++ b/output/roomself_excel/4011.xlsx
@@ -476,10 +476,10 @@
         <v>4460</v>
       </c>
       <c r="E2" t="n">
-        <v>616</v>
+        <v>565</v>
       </c>
       <c r="F2" t="n">
-        <v>487</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>444</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>456</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>1804</v>
       </c>
       <c r="E5" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>7272</v>
       </c>
       <c r="E6" t="n">
-        <v>1076</v>
+        <v>319</v>
       </c>
       <c r="F6" t="n">
-        <v>806</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
         <v>3044</v>
       </c>
       <c r="E8" t="n">
-        <v>470</v>
+        <v>382</v>
       </c>
       <c r="F8" t="n">
-        <v>332</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">

--- a/output/roomself_excel/4011.xlsx
+++ b/output/roomself_excel/4011.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>4460</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>565</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>41</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,12 @@
       <c r="D3" t="n">
         <v>444</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +547,12 @@
       <c r="D4" t="n">
         <v>456</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +569,12 @@
       <c r="D5" t="n">
         <v>1804</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +591,27 @@
       <c r="D6" t="n">
         <v>7272</v>
       </c>
-      <c r="E6" t="n">
-        <v>319</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>251</v>
+        <v>152</v>
+      </c>
+      <c r="G6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>138</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +629,12 @@
       <c r="D7" t="n">
         <v>1340</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +651,27 @@
       <c r="D8" t="n">
         <v>3044</v>
       </c>
-      <c r="E8" t="n">
-        <v>382</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>369</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>91</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +689,27 @@
       <c r="D9" t="n">
         <v>1476</v>
       </c>
-      <c r="E9" t="n">
-        <v>255</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>199</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +727,27 @@
       <c r="D10" t="n">
         <v>444</v>
       </c>
-      <c r="E10" t="n">
-        <v>101</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>52</v>
+      </c>
+      <c r="G10" t="n">
+        <v>42</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>59</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
